--- a/static/sample_documents/Bulk User Creation Format.xlsx
+++ b/static/sample_documents/Bulk User Creation Format.xlsx
@@ -1,154 +1,91 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAC88DC8-15B4-4C32-98FA-E68D209BDF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09516DF1-339F-44A9-9096-440DFBF015E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
-  <si>
-    <t>first_name</t>
-  </si>
-  <si>
-    <t>last_name</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>phone_number</t>
   </si>
   <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
     <t>Alanah</t>
   </si>
   <si>
-    <t>Kigelman</t>
-  </si>
-  <si>
-    <t>akigelman0@list-manage.com</t>
-  </si>
-  <si>
     <t>+251924270472</t>
   </si>
   <si>
-    <t>dB2?t*J4TL`c"720@</t>
-  </si>
-  <si>
-    <t>employee</t>
-  </si>
-  <si>
     <t>Hedwiga</t>
   </si>
   <si>
-    <t>Bertl</t>
-  </si>
-  <si>
-    <t>hbertl1@ihg.com</t>
-  </si>
-  <si>
     <t>+251996030610</t>
   </si>
   <si>
-    <t>oH2{w}()r2qp\d37</t>
-  </si>
-  <si>
     <t>Marillin</t>
   </si>
   <si>
-    <t>Bonehill</t>
-  </si>
-  <si>
-    <t>mbonehill2@goodreads.com</t>
-  </si>
-  <si>
     <t>+251921222298</t>
   </si>
   <si>
-    <t>uK8~kY&gt;io/C@</t>
-  </si>
-  <si>
     <t>Judi</t>
   </si>
   <si>
-    <t>Brimacombe</t>
-  </si>
-  <si>
-    <t>jbrimacombe3@tumblr.com</t>
-  </si>
-  <si>
     <t>+251943578310</t>
   </si>
   <si>
-    <t>lO8&gt;n'&gt;th.oUYwQ@</t>
-  </si>
-  <si>
     <t>Vidovik</t>
   </si>
   <si>
-    <t>Klee</t>
-  </si>
-  <si>
-    <t>vklee4@prlog.org</t>
-  </si>
-  <si>
     <t>+251978556089</t>
   </si>
   <si>
-    <t>aP7+#*b@xs4#!&amp;4F4cP</t>
-  </si>
-  <si>
     <t>Prescott</t>
   </si>
   <si>
-    <t>Maddern</t>
-  </si>
-  <si>
-    <t>pmaddern5@woothemes.com</t>
-  </si>
-  <si>
     <t>+251924744949</t>
   </si>
   <si>
-    <t>nC6{3F@Q?APNQ1P1H</t>
+    <t>height</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>address_street</t>
+  </si>
+  <si>
+    <t>bole</t>
+  </si>
+  <si>
+    <t>english_full_name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Arial"/>
@@ -497,159 +434,138 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="39.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="36" style="1" customWidth="1"/>
-    <col min="4" max="4" width="36.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="50" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.9140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E2" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B3" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E3" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="B4" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E4" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B5" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E5" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B6" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="E6" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="B7" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="E7" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D8" s="2"/>
     </row>
   </sheetData>
